--- a/pricing/output/Trinity模型报价表（内部）.xlsx
+++ b/pricing/output/Trinity模型报价表（内部）.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -605,7 +605,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>有效期：2026-09-30 24:00　|　共 102 款有折扣（生文 72 · 生图 8 · 生视频 22）。底色：生文蓝 · 生图琥珀 · 生视频绿。表头与分册一致（+模态）；不含成本/线路。图/视频多规格刊例见 02/03；达档=企业户累积消耗（按刊例价计）。</t>
+          <t>有效期：2026-09-30 24:00　|　共 86 款有折扣（生文 57 · 生图 7 · 生视频 22）。底色：生文蓝 · 生图琥珀 · 生视频绿。表头与分册一致（+模态）；不含成本/线路。图/视频多规格刊例见 02/03；达档=企业户累积消耗（按刊例价计）。</t>
         </is>
       </c>
     </row>
@@ -674,42 +674,42 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.3-codex-discount</t>
+          <t>gpt-5</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.3 Codex Discount</t>
+          <t>GPT-5</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -718,42 +718,42 @@
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.4-discount</t>
+          <t>gpt-5-nano</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.4 Discount</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -762,42 +762,42 @@
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.4-mini-discount</t>
+          <t>gpt-5.1</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.4 Mini Discount</t>
+          <t>GPT-5.1</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -806,42 +806,42 @@
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.5-discount</t>
+          <t>gpt-5.2</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.5 Discount</t>
+          <t>GPT-5.2</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -850,42 +850,42 @@
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.6-sol-discount</t>
+          <t>gpt-5.3-codex</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol Discount</t>
+          <t>GPT-5.3 Codex</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -894,42 +894,42 @@
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.6-terra-discount</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra Discount</t>
+          <t>GPT-5.4</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.5折</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>7.2折</t>
         </is>
       </c>
     </row>
@@ -938,27 +938,27 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>gpt-5</t>
+          <t>gpt-5.4-mini</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>GPT-5</t>
+          <t>GPT-5.4 Mini</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -982,27 +982,27 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>gpt-5-nano</t>
+          <t>gpt-5.4-nano</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-5.4 nano</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1026,27 +1026,27 @@
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.1</t>
+          <t>gpt-5.4-pro</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.1</t>
+          <t>GPT-5.4 Pro</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>180.00</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1070,27 +1070,27 @@
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.2</t>
+          <t>gpt-5.5</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.2</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1114,27 +1114,27 @@
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.3-codex</t>
+          <t>gpt-5.6-luna</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.3 Codex</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1158,27 +1158,27 @@
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.4</t>
+          <t>gpt-5.6-sol</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.4</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -1199,30 +1199,30 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.4-mini</t>
+          <t>gpt-5.6-terra</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.4 Mini</t>
+          <t>GPT-5.6 Terra</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -1243,45 +1243,49 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.4-nano</t>
+          <t>claude-fable-5</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.4 nano</t>
+          <t>Claude Fable 5</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>8.5折</t>
+          <t>9.5折</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>7.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
     </row>
@@ -1290,42 +1294,42 @@
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.4-pro</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.4 Pro</t>
+          <t>Claude Opus 4.6</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>180.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>8.5折</t>
+          <t>9.5折</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>7.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1338,12 @@
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.5</t>
+          <t>claude-opus-4-7</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>Claude Opus 4.7</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1349,7 +1353,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1359,17 +1363,17 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>8.5折</t>
+          <t>9.5折</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>7.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
     </row>
@@ -1378,42 +1382,42 @@
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.6-luna</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>Claude Opus 4.8</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>8.5折</t>
+          <t>9.5折</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>7.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1426,12 @@
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.6-sol</t>
+          <t>claude-opus-5</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>Claude Opus 5</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1437,7 +1441,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -1447,94 +1451,90 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>8.5折</t>
+          <t>9.5折</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>7.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
-      <c r="B23" s="8" t="n"/>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>gpt-5.6-terra</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>GPT-5.6 Terra</t>
+          <t>Claude Sonnet 4.6</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>8.5折</t>
+          <t>9.5折</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>7.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>claude-fable-5</t>
+          <t>claude-sonnet-5</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Claude Fable 5</t>
+          <t>Claude Sonnet 5</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1555,45 +1555,49 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="n"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>claude-fable-5-discount</t>
+          <t>gemini-2.5-flash</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Claude Fable 5 Discount</t>
+          <t>Gemini 2.5 Flash</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -1602,42 +1606,42 @@
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>gemini-2.5-flash-lite</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Claude Opus 4.6</t>
+          <t>Gemini 2.5 Flash Lite</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -1646,42 +1650,42 @@
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-discount</t>
+          <t>gemini-2.5-pro</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Claude Opus 4.6 Discount</t>
+          <t>Gemini 2.5 Pro</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -1690,42 +1694,42 @@
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>gemini-3-flash-preview</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Claude Opus 4.7</t>
+          <t>Gemini 3 Flash Preview</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -1734,42 +1738,42 @@
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>claude-opus-4-7-discount</t>
+          <t>gemini-3.1-flash-lite</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Claude Opus 4.7 Discount</t>
+          <t>Gemini 3.1 Flash Lite</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -1778,42 +1782,42 @@
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>claude-opus-4-8</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Claude Opus 4.8</t>
+          <t>Gemini 3.1 Pro Preview</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -1822,42 +1826,42 @@
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>claude-opus-4-8-discount</t>
+          <t>gemini-3.1-pro-preview-customtools</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Claude Opus 4.8 Discount</t>
+          <t>Gemini 3.1 Pro Preview Custom Tools</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -1866,42 +1870,42 @@
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>claude-opus-5</t>
+          <t>gemini-3.5-flash</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Claude Opus 5</t>
+          <t>Gemini 3.5 Flash</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -1910,42 +1914,42 @@
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>claude-opus-5-discount</t>
+          <t>gemini-3.6-flash</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Claude Opus 5 Discount</t>
+          <t>Gemini 3.6 Flash</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -1954,130 +1958,134 @@
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>gemini-3.7-flash</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>Gemini 3.7 Flash</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6-discount</t>
+          <t>gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6 Discount</t>
+          <t>Gemini 3.5 Flash Lite</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9折</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.7折</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>8.2折</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
-      <c r="B36" s="7" t="n"/>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>claude-sonnet-5</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Claude Sonnet 5</t>
+          <t>DeepSeek V3.2</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -2086,42 +2094,42 @@
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>claude-sonnet-5-discount</t>
+          <t>deepseek-v4-flash-fast</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Claude Sonnet 5 Discount</t>
+          <t>DeepSeek V4 Flash Fast</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>9.5折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
@@ -2129,47 +2137,47 @@
       <c r="A38" s="7" t="n"/>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>月之暗面</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash</t>
+          <t>kimi-k3</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Flash</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>6.6折</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>6.3折</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>5.8折</t>
         </is>
       </c>
     </row>
@@ -2178,27 +2186,27 @@
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite</t>
+          <t>kimi-k2.5</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Flash Lite</t>
+          <t>Kimi K2.5</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
@@ -2222,27 +2230,27 @@
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>gemini-2.5-pro</t>
+          <t>kimi-k2.6</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Pro</t>
+          <t>Kimi K2.6</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -2263,30 +2271,30 @@
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>gemini-3-flash-preview</t>
+          <t>kimi-k2.7-code</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Gemini 3 Flash Preview</t>
+          <t>Kimi K2.7 Code</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -2307,30 +2315,34 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
-      <c r="B42" s="7" t="n"/>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite</t>
+          <t>minimax-m2.5</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash Lite</t>
+          <t>MiniMax M2.5</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -2354,27 +2366,27 @@
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro Preview</t>
+          <t>MiniMax M2.7</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
@@ -2395,30 +2407,30 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
-      <c r="B44" s="7" t="n"/>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview-customtools</t>
+          <t>minimax-m3</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro Preview Custom Tools</t>
+          <t>MiniMax M3</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
@@ -2439,317 +2451,317 @@
     </row>
     <row r="45">
       <c r="A45" s="7" t="n"/>
-      <c r="B45" s="7" t="n"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash</t>
+          <t>glm-5.2</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>GLM-5.2</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>6.2折</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>6折</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>5.5折</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
-      <c r="B46" s="7" t="n"/>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>gemini-3.6-flash</t>
+          <t>glm-5.3</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Gemini 3.6 Flash</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>6.2折</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>6折</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>5.5折</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
-      <c r="B47" s="7" t="n"/>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>阿里云·通义</t>
+        </is>
+      </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>gemini-3.7-flash</t>
+          <t>qwen-flash</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Gemini 3.7 Flash</t>
+          <t>Qwen Flash</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
-      <c r="B48" s="8" t="n"/>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite</t>
+          <t>qwen-max</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash Lite</t>
+          <t>Qwen Max</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>9折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>8.7折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>DeepSeek</t>
-        </is>
-      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>qwen-plus</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>DeepSeek V3.2</t>
+          <t>Qwen Plus</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
-      <c r="B50" s="8" t="n"/>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash-fast</t>
+          <t>qwen-turbo</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash Fast</t>
+          <t>Qwen Turbo</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>月之暗面</t>
-        </is>
-      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>kimi-k3</t>
+          <t>qwen3.5-flash</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Qwen3.5 Flash</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>6.6折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>6.3折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>5.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
@@ -2758,42 +2770,42 @@
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>kimi-k2.5</t>
+          <t>qwen3.5-plus</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Kimi K2.5</t>
+          <t>Qwen3.5 Plus</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
@@ -2802,134 +2814,130 @@
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>kimi-k2.6</t>
+          <t>qwen3.6-flash</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Kimi K2.6</t>
+          <t>Qwen3.6 Flash</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
-      <c r="B54" s="8" t="n"/>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>kimi-k2.7-code</t>
+          <t>qwen3.6-plus</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Kimi K2.7 Code</t>
+          <t>Qwen3.6 Plus</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>MiniMax</t>
-        </is>
-      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>qwen3.7-flash</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>MiniMax M2.5</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
@@ -2938,163 +2946,163 @@
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>qwen3.7-max</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>MiniMax M2.7</t>
+          <t>Qwen3.7 Max</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
-      <c r="B57" s="8" t="n"/>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>minimax-m3</t>
+          <t>qwen3.7-plus</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>MiniMax M3</t>
+          <t>Qwen3.7 Plus</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>9.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>8.8折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>7.8折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>智谱</t>
-        </is>
-      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>glm-5.2</t>
+          <t>qwen3.8-max</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>GLM-5.2</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
-      <c r="B59" s="7" t="n"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>glm-5.2-discount</t>
+          <t>grok-4.5</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>GLM-5.2 Discount</t>
+          <t>Grok 4.5</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
@@ -3115,30 +3123,30 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
-      <c r="B60" s="7" t="n"/>
+      <c r="B60" s="8" t="n"/>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>glm-5.3</t>
+          <t>grok-4.6</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>Grok 4.6</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
@@ -3158,31 +3166,35 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n"/>
-      <c r="B61" s="8" t="n"/>
+      <c r="A61" s="8" t="n"/>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>glm-5.3-discount</t>
+          <t>codex-auto-review</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>GLM-5.3 Discount</t>
+          <t>Codex Auto Review</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
@@ -3202,952 +3214,964 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n"/>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>阿里云·通义</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>qwen-flash</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Qwen Flash</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>生图</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>gpt-image-2</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>GPT Image 2</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>入 5.00 · 出 30.00 · 缓 1.25</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>8.5折</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
         <is>
           <t>8.2折</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J62" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>7.2折</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
-      <c r="B63" s="7" t="n"/>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>qwen-max</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Qwen Max</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash Image</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>入 0.30 · 出 30.00</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>9折</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>8.7折</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
         <is>
           <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
       <c r="B64" s="7" t="n"/>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>qwen-plus</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Qwen Plus</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Image</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>入 0.50 · 出 60.00</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>9折</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>8.7折</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
         <is>
           <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
-      <c r="B65" s="7" t="n"/>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>qwen-turbo</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Qwen Turbo</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="B65" s="8" t="n"/>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite-image</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash Lite Image</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>入 0.25 · 出 30.00</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>9折</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>8.7折</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr">
         <is>
           <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
-      <c r="B66" s="7" t="n"/>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>qwen3.5-flash</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>Qwen3.5 Flash</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Vidu</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>viduq2-image</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>Vidu Q2 Image</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>0.03（1K）</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>7.5折</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>7折</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>6.4折</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>qwen3.5-plus</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Qwen3.5 Plus</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>grok-imagine-image-pro</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Grok Imagine Image Pro</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>0.05（1K）</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>6.2折</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>6折</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>5.5折</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n"/>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>grok-imagine-image-quality</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Grok Imagine Image Quality</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>0.05（1K）</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>6.2折</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>6折</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>5.5折</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>gemini-omni-flash-preview</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Gemini Omni Flash Preview</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>1.50（输入）</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>9折</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>8.7折</t>
+        </is>
+      </c>
+      <c r="J69" s="14" t="inlineStr">
         <is>
           <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="n"/>
-      <c r="B68" s="7" t="n"/>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>qwen3.6-flash</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>Qwen3.6 Flash</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="n"/>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>qwen3.6-plus</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Qwen3.6 Plus</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
       <c r="B70" s="7" t="n"/>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>qwen3.7-flash</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Qwen3.7 Flash</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>veo-3.1</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>Veo 3.1</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>0.40（720p）</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="14" t="inlineStr">
+        <is>
+          <t>9折</t>
+        </is>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>8.7折</t>
+        </is>
+      </c>
+      <c r="J70" s="14" t="inlineStr">
         <is>
           <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J70" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
       <c r="B71" s="7" t="n"/>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>qwen3.7-max</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>Qwen3.7 Max</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>veo-3.1-fast</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>Veo 3.1 Fast</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>0.10（720p）</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>9折</t>
+        </is>
+      </c>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>8.7折</t>
+        </is>
+      </c>
+      <c r="J71" s="14" t="inlineStr">
         <is>
           <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
-      <c r="B72" s="7" t="n"/>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>qwen3.7-plus</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>Qwen3.7 Plus</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>veo-3.1-lite</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>Veo 3.1 Lite</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>0.05（720p）</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="14" t="inlineStr">
+        <is>
+          <t>9折</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>8.7折</t>
+        </is>
+      </c>
+      <c r="J72" s="14" t="inlineStr">
         <is>
           <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J72" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>qwen3.8-max</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Qwen3.8 Max</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>6.7折</t>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>字节·即梦</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>seedance-2.0-mini-overseas-hc-os</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>Seedance 2.0 Mini Overseas HC</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>3.50（480p）</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>6.2折</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>6折</t>
+        </is>
+      </c>
+      <c r="J73" s="14" t="inlineStr">
+        <is>
+          <t>5.5折</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>grok-4.5</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>Grok 4.5</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>6.2折</t>
-        </is>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>6折</t>
-        </is>
-      </c>
-      <c r="J74" s="6" t="inlineStr">
-        <is>
-          <t>5.5折</t>
+      <c r="B74" s="7" t="n"/>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>seedance-2.0-fast-hc-os</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>Seedance 2.0 Fast HC</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="inlineStr">
+        <is>
+          <t>5.60（480p）</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>8.4折</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>8.1折</t>
+        </is>
+      </c>
+      <c r="J74" s="14" t="inlineStr">
+        <is>
+          <t>7.1折</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
-      <c r="B75" s="8" t="n"/>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>grok-4.6</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>Grok 4.6</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>6.2折</t>
-        </is>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>6折</t>
-        </is>
-      </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>5.5折</t>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>seedance-2.0-os</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>Seedance 2.0</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>7.00（480p）</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>9.8折</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>9.7折</t>
+        </is>
+      </c>
+      <c r="J75" s="14" t="inlineStr">
+        <is>
+          <t>9.4折</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="n"/>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>codex-auto-review</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Codex Auto Review</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>7.80</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>6.2折</t>
-        </is>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>6折</t>
-        </is>
-      </c>
-      <c r="J76" s="6" t="inlineStr">
-        <is>
-          <t>5.5折</t>
+      <c r="A76" s="7" t="n"/>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>seedance-2.0-overseas-hc-os</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>Seedance 2.0 Overseas HC</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>7.00（480p）</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="14" t="inlineStr">
+        <is>
+          <t>9.8折</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>9.7折</t>
+        </is>
+      </c>
+      <c r="J76" s="14" t="inlineStr">
+        <is>
+          <t>9.4折</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>生图</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>gpt-image-2-discount</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>GPT Image 2 Discount</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>0.06（1K）</t>
-        </is>
-      </c>
-      <c r="F77" s="11" t="inlineStr">
+      <c r="A77" s="7" t="n"/>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>minimax-h3</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>MiniMax H3</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>0.08（768p）</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G77" s="11" t="inlineStr">
+      <c r="G77" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H77" s="11" t="inlineStr">
-        <is>
-          <t>6.2折</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>6折</t>
-        </is>
-      </c>
-      <c r="J77" s="11" t="inlineStr">
-        <is>
-          <t>5.5折</t>
+      <c r="H77" s="14" t="inlineStr">
+        <is>
+          <t>9.8折</t>
+        </is>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>9.7折</t>
+        </is>
+      </c>
+      <c r="J77" s="14" t="inlineStr">
+        <is>
+          <t>9.4折</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
-      <c r="B78" s="8" t="n"/>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>gpt-image-2</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>GPT Image 2</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>入 5.00 · 出 30.00 · 缓 1.25</t>
-        </is>
-      </c>
-      <c r="F78" s="11" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>Vidu</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>viduq2</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>Vidu Q2</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>首秒 0.05 + 续秒 0.01/秒 + 5s示例 0.09 + 10s示例 0.14</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G78" s="11" t="inlineStr">
+      <c r="G78" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H78" s="11" t="inlineStr">
-        <is>
-          <t>8.5折</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="J78" s="11" t="inlineStr">
-        <is>
-          <t>7.2折</t>
+      <c r="H78" s="14" t="inlineStr">
+        <is>
+          <t>7.5折</t>
+        </is>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>7折</t>
+        </is>
+      </c>
+      <c r="J78" s="14" t="inlineStr">
+        <is>
+          <t>6.4折</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n"/>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash Image</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>入 0.30 · 出 30.00</t>
-        </is>
-      </c>
-      <c r="F79" s="11" t="inlineStr">
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>viduq2-pro</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>Vidu Q2 Pro</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>首秒 0.04 + 续秒 0.03/秒 + 5s示例 0.13 + 10s示例 0.25</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G79" s="11" t="inlineStr">
+      <c r="G79" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H79" s="11" t="inlineStr">
-        <is>
-          <t>9折</t>
-        </is>
-      </c>
-      <c r="I79" s="11" t="inlineStr">
-        <is>
-          <t>8.7折</t>
-        </is>
-      </c>
-      <c r="J79" s="11" t="inlineStr">
-        <is>
-          <t>8.2折</t>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>7.5折</t>
+        </is>
+      </c>
+      <c r="I79" s="14" t="inlineStr">
+        <is>
+          <t>7折</t>
+        </is>
+      </c>
+      <c r="J79" s="14" t="inlineStr">
+        <is>
+          <t>6.4折</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n"/>
       <c r="B80" s="7" t="n"/>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash Image</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>入 0.50 · 出 60.00</t>
-        </is>
-      </c>
-      <c r="F80" s="11" t="inlineStr">
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>viduq2-turbo</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>Vidu Q2 Turbo</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>首秒 0.03 + 续秒 0.01/秒 + 5s示例 0.07 + 10s示例 0.12</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G80" s="11" t="inlineStr">
+      <c r="G80" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H80" s="11" t="inlineStr">
-        <is>
-          <t>9折</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="inlineStr">
-        <is>
-          <t>8.7折</t>
-        </is>
-      </c>
-      <c r="J80" s="11" t="inlineStr">
-        <is>
-          <t>8.2折</t>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>7.5折</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>7折</t>
+        </is>
+      </c>
+      <c r="J80" s="14" t="inlineStr">
+        <is>
+          <t>6.4折</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n"/>
-      <c r="B81" s="8" t="n"/>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-lite-image</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash Lite Image</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>入 0.25 · 出 30.00</t>
-        </is>
-      </c>
-      <c r="F81" s="11" t="inlineStr">
+      <c r="B81" s="7" t="n"/>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>viduq3</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>Vidu Q3</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>0.04（540p）</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G81" s="11" t="inlineStr">
+      <c r="G81" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H81" s="11" t="inlineStr">
-        <is>
-          <t>9折</t>
-        </is>
-      </c>
-      <c r="I81" s="11" t="inlineStr">
-        <is>
-          <t>8.7折</t>
-        </is>
-      </c>
-      <c r="J81" s="11" t="inlineStr">
-        <is>
-          <t>8.2折</t>
+      <c r="H81" s="14" t="inlineStr">
+        <is>
+          <t>7.5折</t>
+        </is>
+      </c>
+      <c r="I81" s="14" t="inlineStr">
+        <is>
+          <t>7折</t>
+        </is>
+      </c>
+      <c r="J81" s="14" t="inlineStr">
+        <is>
+          <t>6.4折</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n"/>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>Vidu</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>viduq2-image</t>
-        </is>
-      </c>
-      <c r="D82" s="10" t="inlineStr">
-        <is>
-          <t>Vidu Q2 Image</t>
-        </is>
-      </c>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>0.03（1K）</t>
-        </is>
-      </c>
-      <c r="F82" s="11" t="inlineStr">
+      <c r="B82" s="7" t="n"/>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>viduq3-mix</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>Vidu Q3 Mix</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>0.12（720p）</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G82" s="11" t="inlineStr">
+      <c r="G82" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H82" s="11" t="inlineStr">
+      <c r="H82" s="14" t="inlineStr">
         <is>
           <t>7.5折</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr">
+      <c r="I82" s="14" t="inlineStr">
         <is>
           <t>7折</t>
         </is>
       </c>
-      <c r="J82" s="11" t="inlineStr">
+      <c r="J82" s="14" t="inlineStr">
         <is>
           <t>6.4折</t>
         </is>
@@ -4155,120 +4179,108 @@
     </row>
     <row r="83">
       <c r="A83" s="7" t="n"/>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>grok-imagine-image-pro</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>Grok Imagine Image Pro</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>0.05（1K）</t>
-        </is>
-      </c>
-      <c r="F83" s="11" t="inlineStr">
+      <c r="B83" s="7" t="n"/>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>viduq3-pro</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>Vidu Q3 Pro</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>0.05（540p）</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G83" s="11" t="inlineStr">
+      <c r="G83" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H83" s="11" t="inlineStr">
-        <is>
-          <t>6.2折</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="inlineStr">
-        <is>
-          <t>6折</t>
-        </is>
-      </c>
-      <c r="J83" s="11" t="inlineStr">
-        <is>
-          <t>5.5折</t>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>7.5折</t>
+        </is>
+      </c>
+      <c r="I83" s="14" t="inlineStr">
+        <is>
+          <t>7折</t>
+        </is>
+      </c>
+      <c r="J83" s="14" t="inlineStr">
+        <is>
+          <t>6.4折</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="n"/>
-      <c r="B84" s="8" t="n"/>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>grok-imagine-image-quality</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t>Grok Imagine Image Quality</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>0.05（1K）</t>
-        </is>
-      </c>
-      <c r="F84" s="11" t="inlineStr">
+      <c r="A84" s="7" t="n"/>
+      <c r="B84" s="7" t="n"/>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>viduq3-pro-fast</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>Vidu Q3 Pro Fast</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>0.06（720p）</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G84" s="11" t="inlineStr">
+      <c r="G84" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H84" s="11" t="inlineStr">
-        <is>
-          <t>6.2折</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="inlineStr">
-        <is>
-          <t>6折</t>
-        </is>
-      </c>
-      <c r="J84" s="11" t="inlineStr">
-        <is>
-          <t>5.5折</t>
+      <c r="H84" s="14" t="inlineStr">
+        <is>
+          <t>7.5折</t>
+        </is>
+      </c>
+      <c r="I84" s="14" t="inlineStr">
+        <is>
+          <t>7折</t>
+        </is>
+      </c>
+      <c r="J84" s="14" t="inlineStr">
+        <is>
+          <t>6.4折</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t>生视频</t>
-        </is>
-      </c>
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
+      <c r="A85" s="7" t="n"/>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="13" t="inlineStr">
         <is>
-          <t>gemini-omni-flash-preview</t>
+          <t>viduq3-turbo</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>Gemini Omni Flash Preview</t>
+          <t>Vidu Q3 Turbo</t>
         </is>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>1.50（输入）</t>
+          <t>0.04（540p）</t>
         </is>
       </c>
       <c r="F85" s="14" t="inlineStr">
@@ -4283,36 +4295,40 @@
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
-          <t>9折</t>
+          <t>7.5折</t>
         </is>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
-          <t>8.7折</t>
+          <t>7折</t>
         </is>
       </c>
       <c r="J85" s="14" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>6.4折</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n"/>
-      <c r="B86" s="7" t="n"/>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>阿里云·通义</t>
+        </is>
+      </c>
       <c r="C86" s="13" t="inlineStr">
         <is>
-          <t>veo-3.1</t>
+          <t>wan2.7</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>Veo 3.1</t>
+          <t>Wan 2.7</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>0.40（720p）</t>
+          <t>0.10（720p）</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
@@ -4327,36 +4343,40 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>9折</t>
+          <t>9.2折</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>8.7折</t>
+          <t>8.8折</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>7.8折</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n"/>
-      <c r="B87" s="7" t="n"/>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
       <c r="C87" s="13" t="inlineStr">
         <is>
-          <t>veo-3.1-fast</t>
+          <t>grok-imagine-video-1.5</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>Veo 3.1 Fast</t>
+          <t>Grok Imagine Video 1.5</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>0.10（720p）</t>
+          <t>0.08（480p）</t>
         </is>
       </c>
       <c r="F87" s="14" t="inlineStr">
@@ -4371,36 +4391,36 @@
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
-          <t>9折</t>
+          <t>6.2折</t>
         </is>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>8.7折</t>
+          <t>6折</t>
         </is>
       </c>
       <c r="J87" s="14" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>5.5折</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n"/>
-      <c r="B88" s="8" t="n"/>
+      <c r="B88" s="7" t="n"/>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>veo-3.1-lite</t>
+          <t>happyhorse-1.1</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>Veo 3.1 Lite</t>
+          <t>HappyHorse 1.1</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>0.05（720p）</t>
+          <t>0.07（480p）</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
@@ -4415,40 +4435,36 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>9折</t>
+          <t>6.2折</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>8.7折</t>
+          <t>6折</t>
         </is>
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>8.2折</t>
+          <t>5.5折</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
-      <c r="B89" s="12" t="inlineStr">
-        <is>
-          <t>字节·即梦</t>
-        </is>
-      </c>
+      <c r="B89" s="7" t="n"/>
       <c r="C89" s="13" t="inlineStr">
         <is>
-          <t>seedance-2.0-mini-overseas-hc-os</t>
+          <t>happyhorse-1.0</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>Seedance 2.0 Mini Overseas HC</t>
+          <t>HappyHorse 1.0</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>3.50（480p）</t>
+          <t>0.07（480p）</t>
         </is>
       </c>
       <c r="F89" s="14" t="inlineStr">
@@ -4463,36 +4479,36 @@
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
-          <t>6.2折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>6折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J89" s="14" t="inlineStr">
         <is>
-          <t>5.5折</t>
+          <t>6.7折</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="7" t="n"/>
-      <c r="B90" s="7" t="n"/>
+      <c r="A90" s="8" t="n"/>
+      <c r="B90" s="8" t="n"/>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>seedance-2.0-fast-hc-os</t>
+          <t>happyhorse-1.0-video-edit</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>Seedance 2.0 Fast HC</t>
+          <t>HappyHorse 1.0 Video Edit</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>5.60（480p）</t>
+          <t>0.14（720p）</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
@@ -4507,763 +4523,42 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>8.4折</t>
+          <t>8.2折</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>8.1折</t>
+          <t>7.6折</t>
         </is>
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>7.1折</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="n"/>
-      <c r="B91" s="7" t="n"/>
-      <c r="C91" s="13" t="inlineStr">
-        <is>
-          <t>seedance-2.0-os</t>
-        </is>
-      </c>
-      <c r="D91" s="13" t="inlineStr">
-        <is>
-          <t>Seedance 2.0</t>
-        </is>
-      </c>
-      <c r="E91" s="14" t="inlineStr">
-        <is>
-          <t>7.00（480p）</t>
-        </is>
-      </c>
-      <c r="F91" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G91" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H91" s="14" t="inlineStr">
-        <is>
-          <t>9.8折</t>
-        </is>
-      </c>
-      <c r="I91" s="14" t="inlineStr">
-        <is>
-          <t>9.7折</t>
-        </is>
-      </c>
-      <c r="J91" s="14" t="inlineStr">
-        <is>
-          <t>9.4折</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="7" t="n"/>
-      <c r="B92" s="8" t="n"/>
-      <c r="C92" s="13" t="inlineStr">
-        <is>
-          <t>seedance-2.0-overseas-hc-os</t>
-        </is>
-      </c>
-      <c r="D92" s="13" t="inlineStr">
-        <is>
-          <t>Seedance 2.0 Overseas HC</t>
-        </is>
-      </c>
-      <c r="E92" s="14" t="inlineStr">
-        <is>
-          <t>7.00（480p）</t>
-        </is>
-      </c>
-      <c r="F92" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G92" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H92" s="14" t="inlineStr">
-        <is>
-          <t>9.8折</t>
-        </is>
-      </c>
-      <c r="I92" s="14" t="inlineStr">
-        <is>
-          <t>9.7折</t>
-        </is>
-      </c>
-      <c r="J92" s="14" t="inlineStr">
-        <is>
-          <t>9.4折</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="n"/>
-      <c r="B93" s="13" t="inlineStr">
-        <is>
-          <t>MiniMax</t>
-        </is>
-      </c>
-      <c r="C93" s="13" t="inlineStr">
-        <is>
-          <t>minimax-h3</t>
-        </is>
-      </c>
-      <c r="D93" s="13" t="inlineStr">
-        <is>
-          <t>MiniMax H3</t>
-        </is>
-      </c>
-      <c r="E93" s="14" t="inlineStr">
-        <is>
-          <t>0.08（768p）</t>
-        </is>
-      </c>
-      <c r="F93" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G93" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H93" s="14" t="inlineStr">
-        <is>
-          <t>9.8折</t>
-        </is>
-      </c>
-      <c r="I93" s="14" t="inlineStr">
-        <is>
-          <t>9.7折</t>
-        </is>
-      </c>
-      <c r="J93" s="14" t="inlineStr">
-        <is>
-          <t>9.4折</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="n"/>
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>Vidu</t>
-        </is>
-      </c>
-      <c r="C94" s="13" t="inlineStr">
-        <is>
-          <t>viduq2</t>
-        </is>
-      </c>
-      <c r="D94" s="13" t="inlineStr">
-        <is>
-          <t>Vidu Q2</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="inlineStr">
-        <is>
-          <t>首秒 0.05 + 续秒 0.01/秒 + 5s示例 0.09 + 10s示例 0.14</t>
-        </is>
-      </c>
-      <c r="F94" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G94" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H94" s="14" t="inlineStr">
-        <is>
-          <t>7.5折</t>
-        </is>
-      </c>
-      <c r="I94" s="14" t="inlineStr">
-        <is>
-          <t>7折</t>
-        </is>
-      </c>
-      <c r="J94" s="14" t="inlineStr">
-        <is>
-          <t>6.4折</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="n"/>
-      <c r="B95" s="7" t="n"/>
-      <c r="C95" s="13" t="inlineStr">
-        <is>
-          <t>viduq2-pro</t>
-        </is>
-      </c>
-      <c r="D95" s="13" t="inlineStr">
-        <is>
-          <t>Vidu Q2 Pro</t>
-        </is>
-      </c>
-      <c r="E95" s="14" t="inlineStr">
-        <is>
-          <t>首秒 0.04 + 续秒 0.03/秒 + 5s示例 0.13 + 10s示例 0.25</t>
-        </is>
-      </c>
-      <c r="F95" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H95" s="14" t="inlineStr">
-        <is>
-          <t>7.5折</t>
-        </is>
-      </c>
-      <c r="I95" s="14" t="inlineStr">
-        <is>
-          <t>7折</t>
-        </is>
-      </c>
-      <c r="J95" s="14" t="inlineStr">
-        <is>
-          <t>6.4折</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="7" t="n"/>
-      <c r="B96" s="7" t="n"/>
-      <c r="C96" s="13" t="inlineStr">
-        <is>
-          <t>viduq2-turbo</t>
-        </is>
-      </c>
-      <c r="D96" s="13" t="inlineStr">
-        <is>
-          <t>Vidu Q2 Turbo</t>
-        </is>
-      </c>
-      <c r="E96" s="14" t="inlineStr">
-        <is>
-          <t>首秒 0.03 + 续秒 0.01/秒 + 5s示例 0.07 + 10s示例 0.12</t>
-        </is>
-      </c>
-      <c r="F96" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G96" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H96" s="14" t="inlineStr">
-        <is>
-          <t>7.5折</t>
-        </is>
-      </c>
-      <c r="I96" s="14" t="inlineStr">
-        <is>
-          <t>7折</t>
-        </is>
-      </c>
-      <c r="J96" s="14" t="inlineStr">
-        <is>
-          <t>6.4折</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="n"/>
-      <c r="B97" s="7" t="n"/>
-      <c r="C97" s="13" t="inlineStr">
-        <is>
-          <t>viduq3</t>
-        </is>
-      </c>
-      <c r="D97" s="13" t="inlineStr">
-        <is>
-          <t>Vidu Q3</t>
-        </is>
-      </c>
-      <c r="E97" s="14" t="inlineStr">
-        <is>
-          <t>0.04（540p）</t>
-        </is>
-      </c>
-      <c r="F97" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G97" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H97" s="14" t="inlineStr">
-        <is>
-          <t>7.5折</t>
-        </is>
-      </c>
-      <c r="I97" s="14" t="inlineStr">
-        <is>
-          <t>7折</t>
-        </is>
-      </c>
-      <c r="J97" s="14" t="inlineStr">
-        <is>
-          <t>6.4折</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="n"/>
-      <c r="B98" s="7" t="n"/>
-      <c r="C98" s="13" t="inlineStr">
-        <is>
-          <t>viduq3-mix</t>
-        </is>
-      </c>
-      <c r="D98" s="13" t="inlineStr">
-        <is>
-          <t>Vidu Q3 Mix</t>
-        </is>
-      </c>
-      <c r="E98" s="14" t="inlineStr">
-        <is>
-          <t>0.12（720p）</t>
-        </is>
-      </c>
-      <c r="F98" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G98" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H98" s="14" t="inlineStr">
-        <is>
-          <t>7.5折</t>
-        </is>
-      </c>
-      <c r="I98" s="14" t="inlineStr">
-        <is>
-          <t>7折</t>
-        </is>
-      </c>
-      <c r="J98" s="14" t="inlineStr">
-        <is>
-          <t>6.4折</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="7" t="n"/>
-      <c r="B99" s="7" t="n"/>
-      <c r="C99" s="13" t="inlineStr">
-        <is>
-          <t>viduq3-pro</t>
-        </is>
-      </c>
-      <c r="D99" s="13" t="inlineStr">
-        <is>
-          <t>Vidu Q3 Pro</t>
-        </is>
-      </c>
-      <c r="E99" s="14" t="inlineStr">
-        <is>
-          <t>0.05（540p）</t>
-        </is>
-      </c>
-      <c r="F99" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H99" s="14" t="inlineStr">
-        <is>
-          <t>7.5折</t>
-        </is>
-      </c>
-      <c r="I99" s="14" t="inlineStr">
-        <is>
-          <t>7折</t>
-        </is>
-      </c>
-      <c r="J99" s="14" t="inlineStr">
-        <is>
-          <t>6.4折</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="n"/>
-      <c r="B100" s="7" t="n"/>
-      <c r="C100" s="13" t="inlineStr">
-        <is>
-          <t>viduq3-pro-fast</t>
-        </is>
-      </c>
-      <c r="D100" s="13" t="inlineStr">
-        <is>
-          <t>Vidu Q3 Pro Fast</t>
-        </is>
-      </c>
-      <c r="E100" s="14" t="inlineStr">
-        <is>
-          <t>0.06（720p）</t>
-        </is>
-      </c>
-      <c r="F100" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G100" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H100" s="14" t="inlineStr">
-        <is>
-          <t>7.5折</t>
-        </is>
-      </c>
-      <c r="I100" s="14" t="inlineStr">
-        <is>
-          <t>7折</t>
-        </is>
-      </c>
-      <c r="J100" s="14" t="inlineStr">
-        <is>
-          <t>6.4折</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="7" t="n"/>
-      <c r="B101" s="8" t="n"/>
-      <c r="C101" s="13" t="inlineStr">
-        <is>
-          <t>viduq3-turbo</t>
-        </is>
-      </c>
-      <c r="D101" s="13" t="inlineStr">
-        <is>
-          <t>Vidu Q3 Turbo</t>
-        </is>
-      </c>
-      <c r="E101" s="14" t="inlineStr">
-        <is>
-          <t>0.04（540p）</t>
-        </is>
-      </c>
-      <c r="F101" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G101" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H101" s="14" t="inlineStr">
-        <is>
-          <t>7.5折</t>
-        </is>
-      </c>
-      <c r="I101" s="14" t="inlineStr">
-        <is>
-          <t>7折</t>
-        </is>
-      </c>
-      <c r="J101" s="14" t="inlineStr">
-        <is>
-          <t>6.4折</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="7" t="n"/>
-      <c r="B102" s="13" t="inlineStr">
-        <is>
-          <t>阿里云·通义</t>
-        </is>
-      </c>
-      <c r="C102" s="13" t="inlineStr">
-        <is>
-          <t>wan2.7</t>
-        </is>
-      </c>
-      <c r="D102" s="13" t="inlineStr">
-        <is>
-          <t>Wan 2.7</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="inlineStr">
-        <is>
-          <t>0.10（720p）</t>
-        </is>
-      </c>
-      <c r="F102" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G102" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H102" s="14" t="inlineStr">
-        <is>
-          <t>9.2折</t>
-        </is>
-      </c>
-      <c r="I102" s="14" t="inlineStr">
-        <is>
-          <t>8.8折</t>
-        </is>
-      </c>
-      <c r="J102" s="14" t="inlineStr">
-        <is>
-          <t>7.8折</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="7" t="n"/>
-      <c r="B103" s="12" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C103" s="13" t="inlineStr">
-        <is>
-          <t>grok-imagine-video-1.5</t>
-        </is>
-      </c>
-      <c r="D103" s="13" t="inlineStr">
-        <is>
-          <t>Grok Imagine Video 1.5</t>
-        </is>
-      </c>
-      <c r="E103" s="14" t="inlineStr">
-        <is>
-          <t>0.08（480p）</t>
-        </is>
-      </c>
-      <c r="F103" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G103" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H103" s="14" t="inlineStr">
-        <is>
-          <t>6.2折</t>
-        </is>
-      </c>
-      <c r="I103" s="14" t="inlineStr">
-        <is>
-          <t>6折</t>
-        </is>
-      </c>
-      <c r="J103" s="14" t="inlineStr">
-        <is>
-          <t>5.5折</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="7" t="n"/>
-      <c r="B104" s="7" t="n"/>
-      <c r="C104" s="13" t="inlineStr">
-        <is>
-          <t>happyhorse-1.1</t>
-        </is>
-      </c>
-      <c r="D104" s="13" t="inlineStr">
-        <is>
-          <t>HappyHorse 1.1</t>
-        </is>
-      </c>
-      <c r="E104" s="14" t="inlineStr">
-        <is>
-          <t>0.07（480p）</t>
-        </is>
-      </c>
-      <c r="F104" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G104" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H104" s="14" t="inlineStr">
-        <is>
-          <t>6.2折</t>
-        </is>
-      </c>
-      <c r="I104" s="14" t="inlineStr">
-        <is>
-          <t>6折</t>
-        </is>
-      </c>
-      <c r="J104" s="14" t="inlineStr">
-        <is>
-          <t>5.5折</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="7" t="n"/>
-      <c r="B105" s="7" t="n"/>
-      <c r="C105" s="13" t="inlineStr">
-        <is>
-          <t>happyhorse-1.0</t>
-        </is>
-      </c>
-      <c r="D105" s="13" t="inlineStr">
-        <is>
-          <t>HappyHorse 1.0</t>
-        </is>
-      </c>
-      <c r="E105" s="14" t="inlineStr">
-        <is>
-          <t>0.07（480p）</t>
-        </is>
-      </c>
-      <c r="F105" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G105" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H105" s="14" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I105" s="14" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J105" s="14" t="inlineStr">
-        <is>
           <t>6.7折</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="8" t="n"/>
-      <c r="B106" s="8" t="n"/>
-      <c r="C106" s="13" t="inlineStr">
-        <is>
-          <t>happyhorse-1.0-video-edit</t>
-        </is>
-      </c>
-      <c r="D106" s="13" t="inlineStr">
-        <is>
-          <t>HappyHorse 1.0 Video Edit</t>
-        </is>
-      </c>
-      <c r="E106" s="14" t="inlineStr">
-        <is>
-          <t>0.14（720p）</t>
-        </is>
-      </c>
-      <c r="F106" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G106" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H106" s="14" t="inlineStr">
-        <is>
-          <t>8.2折</t>
-        </is>
-      </c>
-      <c r="I106" s="14" t="inlineStr">
-        <is>
-          <t>7.6折</t>
-        </is>
-      </c>
-      <c r="J106" s="14" t="inlineStr">
-        <is>
-          <t>6.7折</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="A77:A84"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="B94:B101"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B38:B48"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="A85:A106"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B103:B106"/>
+  <mergeCells count="20">
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B73:B76"/>
+    <mergeCell ref="B47:B58"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="A62:A68"/>
+    <mergeCell ref="A5:A61"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B62:B73"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="B24:B37"/>
-    <mergeCell ref="A5:A76"/>
-    <mergeCell ref="B89:B92"/>
+    <mergeCell ref="B69:B72"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B87:B90"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B25:B35"/>
+    <mergeCell ref="B5:B17"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B78:B85"/>
+    <mergeCell ref="B18:B24"/>
+    <mergeCell ref="A69:A90"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="B85:B88"/>
-    <mergeCell ref="B5:B23"/>
+    <mergeCell ref="B59:B60"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
